--- a/local1.xlsx
+++ b/local1.xlsx
@@ -3429,7 +3429,11 @@
           <t>张利强-毕业证书.pdf</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>张利强-硕士学位.pdf</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>张利强-学信网截图.pdf</t>
@@ -3449,7 +3453,7 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>张利强-交换技术中级.pdf，张利强-硕士学位.pdf</t>
+          <t>张利强-交换技术中级.pdf</t>
         </is>
       </c>
     </row>
@@ -3704,8 +3708,16 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>张文俊-本科-学历.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>张文俊-本科-学位.jpg</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
           <t>张文俊-学信网学历查询.pdf</t>
@@ -3719,11 +3731,7 @@
           <t>高级网络与信息安全工程师-张文俊.pdf</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>张文俊-本科-学位.jpg，张文俊-本科-学历.jpg</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
